--- a/20251229_new_progress/Code/paper_data_newdata/main_paper_results/01_model_performance/03_ridge_lasso_regularized/outputs/ridge_lasso_regularized_performance.xlsx
+++ b/20251229_new_progress/Code/paper_data_newdata/main_paper_results/01_model_performance/03_ridge_lasso_regularized/outputs/ridge_lasso_regularized_performance.xlsx
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>17</v>
@@ -719,74 +719,74 @@
         <v>1321</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O2" s="3" t="inlineStr"/>
       <c r="P2" s="3" t="n">
         <v>0.0630957344480193</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.7355168496781522</v>
+        <v>0.7478227943960621</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.7564929405612689</v>
+        <v>0.7672142607479903</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.7545201668984701</v>
+        <v>0.7672142607479903</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>0.7584760573226145</v>
+        <v>0.7672142607479903</v>
       </c>
       <c r="U2" s="3" t="n">
-        <v>0.8139428232027202</v>
+        <v>0.8213421793837302</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>0.7418622255866768</v>
+        <v>0.7426192278576835</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>0.7643400138217</v>
+        <v>0.7629009762900977</v>
       </c>
       <c r="X2" s="3" t="n">
-        <v>0.7554644808743169</v>
+        <v>0.760778859527121</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.7734265734265734</v>
+        <v>0.765034965034965</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>0.8170070853239171</v>
+        <v>0.8319670428581319</v>
       </c>
       <c r="AA2" s="3" t="n">
-        <v>0.7340574174752827</v>
+        <v>0.7404201362604088</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>0.0161597442412721</v>
+        <v>0.0136379335533874</v>
       </c>
       <c r="AC2" s="3" t="n">
-        <v>0.7553490746860423</v>
+        <v>0.7603958222391946</v>
       </c>
       <c r="AD2" s="3" t="n">
-        <v>0.0159068271055397</v>
+        <v>0.014868997842478</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.752439761767649</v>
+        <v>0.7597800250668976</v>
       </c>
       <c r="AF2" s="3" t="n">
-        <v>0.013271746274976</v>
+        <v>0.007957645305634699</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>0.7583787162558112</v>
+        <v>0.7611743563698872</v>
       </c>
       <c r="AH2" s="3" t="n">
-        <v>0.0202653710756137</v>
+        <v>0.022536628524725</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>0.8106423133969024</v>
+        <v>0.8196197852234338</v>
       </c>
       <c r="AJ2" s="3" t="n">
-        <v>0.0139276079276346</v>
+        <v>0.0137581860107653</v>
       </c>
       <c r="AK2" s="3" t="inlineStr">
         <is>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>17</v>
@@ -842,74 +842,74 @@
         <v>1321</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="n">
-        <v>0.0158489319246111</v>
+        <v>0.01</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.7387353275274517</v>
+        <v>0.743847027641045</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.7597493036211699</v>
+        <v>0.7644088455511057</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>0.7568505029483177</v>
+        <v>0.7616238723108952</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>0.7626703949667948</v>
+        <v>0.7672142607479903</v>
       </c>
       <c r="U3" s="3" t="n">
-        <v>0.8142491836763863</v>
+        <v>0.8214311134326363</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>0.7373202119606359</v>
+        <v>0.74110522331567</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>0.7611837577426015</v>
+        <v>0.7618384401114207</v>
       </c>
       <c r="X3" s="3" t="n">
-        <v>0.7493224932249323</v>
+        <v>0.7586685159500693</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>0.7734265734265734</v>
+        <v>0.765034965034965</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>0.8168224514759168</v>
+        <v>0.8320247409356321</v>
       </c>
       <c r="AA3" s="3" t="n">
-        <v>0.734967425962884</v>
+        <v>0.7402682770169523</v>
       </c>
       <c r="AB3" s="3" t="n">
-        <v>0.0128607019591378</v>
+        <v>0.0121210167261209</v>
       </c>
       <c r="AC3" s="3" t="n">
-        <v>0.7567322838522765</v>
+        <v>0.7606541839905891</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>0.0129914500135163</v>
+        <v>0.0131420697880074</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.7521797362839285</v>
+        <v>0.7588996885343929</v>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>0.0102633240129441</v>
+        <v>0.0076243454772415</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>0.7614556393327343</v>
+        <v>0.7625733484392703</v>
       </c>
       <c r="AH3" s="3" t="n">
-        <v>0.0180984172802626</v>
+        <v>0.0203017670237043</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>0.8107380738521348</v>
+        <v>0.8196304550378182</v>
       </c>
       <c r="AJ3" s="3" t="n">
-        <v>0.0138879031907903</v>
+        <v>0.0141622793103983</v>
       </c>
       <c r="AK3" s="3" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>21</v>
@@ -965,74 +965,74 @@
         <v>1321</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O4" s="3" t="inlineStr"/>
       <c r="P4" s="3" t="n">
-        <v>0.3981071705534973</v>
+        <v>0.2511886431509582</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.6550549034456645</v>
+        <v>0.6573267701628172</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.6739441660701503</v>
+        <v>0.6756272401433692</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.6703453186187255</v>
+        <v>0.6729739378793288</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>0.6775818639798489</v>
+        <v>0.6783015473191796</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>0.7114842541594922</v>
+        <v>0.7150506833325738</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>0.6525359576078729</v>
+        <v>0.6548069644208933</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>0.6719085060757684</v>
+        <v>0.6742857142857143</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>0.6676136363636364</v>
+        <v>0.6695035460992907</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0.6762589928057554</v>
+        <v>0.6791366906474821</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>0.7174086928540235</v>
+        <v>0.7179350449352977</v>
       </c>
       <c r="AA4" s="3" t="n">
-        <v>0.6501624113963251</v>
+        <v>0.6513746473057601</v>
       </c>
       <c r="AB4" s="3" t="n">
-        <v>0.0112588072095183</v>
+        <v>0.0143637381602052</v>
       </c>
       <c r="AC4" s="3" t="n">
-        <v>0.6696133289017522</v>
+        <v>0.6708998877631803</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>0.0109597336016012</v>
+        <v>0.014657958188124</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.6654255427530236</v>
+        <v>0.6663409082623397</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.0102517084517106</v>
+        <v>0.012397425500657</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.673867683950822</v>
+        <v>0.675599693156138</v>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>0.012039812157721</v>
+        <v>0.0182188715522267</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>0.7071292704983907</v>
+        <v>0.7099569243042742</v>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>0.0101495452637152</v>
+        <v>0.0109006072964267</v>
       </c>
       <c r="AK4" s="3" t="inlineStr">
         <is>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>21</v>
@@ -1088,74 +1088,74 @@
         <v>1321</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="n">
-        <v>0.0158489319246111</v>
+        <v>0.0063095734448019</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.6542976145399469</v>
+        <v>0.6573267701628172</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.6738120757413362</v>
+        <v>0.676670239371204</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.669031571479248</v>
+        <v>0.6718694572543455</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>0.6786613889888449</v>
+        <v>0.6815401223461677</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>0.7113765748104793</v>
+        <v>0.7146185282950132</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>0.6563209689629069</v>
+        <v>0.6548069644208933</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.6757142857142857</v>
+        <v>0.6756756756756757</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>0.6709219858156028</v>
+        <v>0.6680731364275668</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0.6805755395683454</v>
+        <v>0.6834532374100719</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0.7176638242121958</v>
+        <v>0.7178522996299446</v>
       </c>
       <c r="AA5" s="3" t="n">
-        <v>0.6489509783680867</v>
+        <v>0.6507684720023856</v>
       </c>
       <c r="AB5" s="3" t="n">
-        <v>0.0111683292247742</v>
+        <v>0.0128357205746989</v>
       </c>
       <c r="AC5" s="3" t="n">
-        <v>0.6684607619169196</v>
+        <v>0.6710782008674138</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>0.0111096934053183</v>
+        <v>0.013364198441203</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.664276158654306</v>
+        <v>0.665022039177015</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.0099275160096669</v>
+        <v>0.0108649675924337</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.672717019467999</v>
+        <v>0.6773258972073062</v>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>0.012724047638888</v>
+        <v>0.0172717753893653</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>0.7073519039995486</v>
+        <v>0.7100636559204856</v>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>0.0101536415678938</v>
+        <v>0.0109608493042482</v>
       </c>
       <c r="AK5" s="3" t="inlineStr">
         <is>
@@ -1174,12 +1174,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.6808218023326682</v>
+        <v>0.6153864917696557</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>15.85505078243633</v>
+        <v>14.58186760401076</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.5309076913222321</v>
+        <v>0.4090879938446025</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>12.36383496806257</v>
+        <v>9.693529260738488</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1286,18 +1286,18 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_B</t>
+          <t>feature_v8_03-v8_06</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.3247272544633885</v>
+        <v>0.3278400636691858</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7.56228295321603</v>
+        <v>7.768321969446013</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.2972268042288374</v>
+        <v>0.2865023313530799</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>6.921849533612321</v>
+        <v>6.788805279129842</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -1342,14 +1342,14 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>feature_v1_male</t>
+          <t>feature_v54_B</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.2771443473979836</v>
+        <v>0.2839675151373934</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>6.454167135959478</v>
+        <v>6.728741636277774</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -1370,14 +1370,14 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>feature_v5</t>
+          <t>feature_v1_male</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.2667717969891616</v>
+        <v>0.2798344047853434</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>6.212610075195882</v>
+        <v>6.630805674483995</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1398,18 +1398,18 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>feature_v26_B</t>
+          <t>feature_v5</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.2259702649572769</v>
+        <v>0.2274605061365779</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>5.262419643352697</v>
+        <v>5.389781917517881</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1426,18 +1426,18 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_E</t>
+          <t>feature_v26_B</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.2186433461126733</v>
+        <v>0.2196767965352496</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>5.091789575452466</v>
+        <v>5.205343317723068</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1454,18 +1454,18 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>feature_v38</t>
+          <t>feature_v54_E</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.1442060122236839</v>
+        <v>0.2170699673278155</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>3.358285000723213</v>
+        <v>5.143573293717893</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.1441291664893662</v>
+        <v>0.1241498883321071</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>3.356495409062302</v>
+        <v>2.94178903652167</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1510,18 +1510,18 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>feature_v6</t>
+          <t>feature_v27_B</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.1330839946161186</v>
+        <v>0.1187511129475481</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>3.099274267860499</v>
+        <v>2.813862556278261</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1538,18 +1538,18 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>feature_v27_B</t>
+          <t>feature_v38</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.1267433703640473</v>
+        <v>0.1032861248372195</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2.951613133677524</v>
+        <v>2.447412508806596</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1566,14 +1566,14 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>feature_v34</t>
+          <t>feature_v6</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.1008153313975246</v>
+        <v>0.1031365538316713</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>2.347798195473862</v>
+        <v>2.443868354637677</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1594,18 +1594,18 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>feature_v36</t>
+          <t>feature_v12</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.0997087125668607</v>
+        <v>0.09235938549930101</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>2.322027138059337</v>
+        <v>2.188498365418633</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1622,18 +1622,18 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>feature_v49</t>
+          <t>feature_v54_D</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.0929488195496951</v>
+        <v>0.084542135993254</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2.164602028135158</v>
+        <v>2.003265022065749</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1650,18 +1650,18 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>feature_v42</t>
+          <t>feature_v49</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.0911089184456108</v>
+        <v>0.0823517238547483</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2.121754214889507</v>
+        <v>1.951362193145896</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0.0771390266012678</v>
+        <v>0.080196317952242</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1.796421882907324</v>
+        <v>1.900288853182148</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1706,14 +1706,14 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_D</t>
+          <t>feature_v36</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.0670273610652735</v>
+        <v>0.0691110658413045</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1.560940336900862</v>
+        <v>1.637618676308529</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>feature_v40</t>
+          <t>feature_v42</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.064239272875335</v>
+        <v>0.0681062976212063</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.496011041619885</v>
+        <v>1.613810228521422</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1762,18 +1762,18 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_F</t>
+          <t>feature_v40</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0.0621389189742859</v>
+        <v>0.0654067112959775</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1.447097775845899</v>
+        <v>1.549842281700093</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1790,18 +1790,18 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>feature_v25_B</t>
+          <t>feature_v54_F</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0.052884460127132</v>
+        <v>0.0635983191716923</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1.231578950680697</v>
+        <v>1.506991593741977</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1818,18 +1818,18 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>feature_v27_A</t>
+          <t>feature_v26_A</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.0449631836474659</v>
+        <v>0.0477933947739358</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.04710741875191</v>
+        <v>1.132486598683116</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1846,14 +1846,14 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>feature_v26_A</t>
+          <t>feature_v23_B</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0.0430771804167657</v>
+        <v>0.0452691952147773</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>1.003185974262123</v>
+        <v>1.072674522418806</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -1874,18 +1874,18 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>feature_v23_B</t>
+          <t>feature_v27_A</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.0426382166040368</v>
+        <v>0.0403621195612183</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0.9929633381499696</v>
+        <v>0.9563990947647248</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1902,14 +1902,14 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>feature_v19</t>
+          <t>feature_v25_B</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.0231898515089361</v>
+        <v>0.0374302157688039</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0.5400477365025439</v>
+        <v>0.8869262780869632</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -1930,18 +1930,18 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>feature_v25_A</t>
+          <t>feature_v54_C</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.022353135756453</v>
+        <v>0.0352105922833573</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.5205622107737417</v>
+        <v>0.834331272788002</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1958,14 +1958,14 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>feature_v25_C</t>
+          <t>feature_v9</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.0168052148996395</v>
+        <v>0.0183318701996152</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.3913616378480007</v>
+        <v>0.434382144814381</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -1986,18 +1986,18 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>feature_v23_A</t>
+          <t>feature_v34</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.0135343892784774</v>
+        <v>0.0170814921085077</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.3151903017563293</v>
+        <v>0.4047538575130874</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2014,18 +2014,18 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>feature_v3</t>
+          <t>feature_v23_A</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.0073195543830187</v>
+        <v>0.0156171728601008</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>0.1704585635329875</v>
+        <v>0.3700561355191096</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2042,18 +2042,18 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_C</t>
+          <t>feature_v25_A</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.0017699496062033</v>
+        <v>0.0149015381834363</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0.0412187752985537</v>
+        <v>0.3530988407985964</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2065,19 +2065,19 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>lasso</t>
+          <t>ridge</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>feature_v52</t>
+          <t>feature_v25_C</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.7469806204458977</v>
+        <v>0.0135397595741134</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>18.66380635517925</v>
+        <v>0.3208308666836329</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -2093,23 +2093,23 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>lasso</t>
+          <t>ridge</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_A</t>
+          <t>feature_v19</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0.5965119993603074</v>
+        <v>0.0121753517254081</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>14.90424803518439</v>
+        <v>0.2885005915252039</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2121,23 +2121,23 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>lasso</t>
+          <t>ridge</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_B</t>
+          <t>feature_v3</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.3429606191195953</v>
+        <v>0.0006828384530402</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>8.569098591713896</v>
+        <v>0.0161801730300052</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2154,18 +2154,18 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>feature_v28</t>
+          <t>feature_v52</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0.303312182719127</v>
+        <v>0.7165826024281782</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>7.578456105136058</v>
+        <v>17.55726416821722</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2182,18 +2182,18 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>feature_v1_male</t>
+          <t>feature_v54_A</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.2740131534022609</v>
+        <v>0.4892620869076461</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>6.846400420427281</v>
+        <v>11.98759735196301</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2210,18 +2210,18 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>feature_v5</t>
+          <t>feature_v8_03-v8_06</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0.2708460447466573</v>
+        <v>0.3575124149729877</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>6.767268109580031</v>
+        <v>8.759548294681307</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2238,18 +2238,18 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>feature_v26_B</t>
+          <t>feature_v54_B</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>0.2150959408656728</v>
+        <v>0.3102950064170995</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>5.37431477901744</v>
+        <v>7.602656524569627</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2266,18 +2266,18 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_E</t>
+          <t>feature_v28</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>0.2034152490156939</v>
+        <v>0.3059010952021421</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>5.082464944074746</v>
+        <v>7.494999626856387</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2294,18 +2294,18 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>feature_v38</t>
+          <t>feature_v1_male</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0.1501920742829295</v>
+        <v>0.2837673408804152</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>3.752648614666867</v>
+        <v>6.952692054297187</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2322,18 +2322,18 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>feature_v22</t>
+          <t>feature_v5</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.1360084074375641</v>
+        <v>0.2360859638522293</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>3.3982602889694</v>
+        <v>5.784432415350495</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>feature_v6</t>
+          <t>feature_v26_B</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>0.1237266814408501</v>
+        <v>0.2238347570358374</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>3.091393217139333</v>
+        <v>5.484260915615524</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -2378,14 +2378,14 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>feature_v27_B</t>
+          <t>feature_v54_E</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>0.105593117422073</v>
+        <v>0.2133435410475827</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>2.638314090168575</v>
+        <v>5.227211623702142</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -2406,14 +2406,14 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>feature_v36</t>
+          <t>feature_v22</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>0.0981837283174256</v>
+        <v>0.1150815122907136</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>2.453185587936797</v>
+        <v>2.819656108478448</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
@@ -2434,14 +2434,14 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>feature_v34</t>
+          <t>feature_v38</t>
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>0.0916781999176671</v>
+        <v>0.1077395986064514</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>2.290640645045595</v>
+        <v>2.639769075751109</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -2462,18 +2462,18 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>feature_v42</t>
+          <t>feature_v27_B</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0.08339544957656291</v>
+        <v>0.1072959940985359</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>2.083690632925622</v>
+        <v>2.628900152189061</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2490,18 +2490,18 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>feature_v49</t>
+          <t>feature_v6</t>
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>0.083173154557692</v>
+        <v>0.0971616110866243</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>2.078136444406714</v>
+        <v>2.380593761384857</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2518,18 +2518,18 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>feature_v40</t>
+          <t>feature_v12</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.0521634840424822</v>
+        <v>0.07636454972971329</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.303339254503303</v>
+        <v>1.871037013944137</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2546,18 +2546,18 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>feature_v23_C</t>
+          <t>feature_v49</t>
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>0.0421530729371397</v>
+        <v>0.0724936333981769</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>1.053222492043894</v>
+        <v>1.776194213720472</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2574,18 +2574,18 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_F</t>
+          <t>feature_v36</t>
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>0.0345470592517995</v>
+        <v>0.0643645438289913</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>0.8631811942210765</v>
+        <v>1.577020283834842</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2602,18 +2602,18 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>feature_v25_B</t>
+          <t>feature_v54_D</t>
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>0.0165813103276785</v>
+        <v>0.0592009475825757</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>0.4142950387202719</v>
+        <v>1.450505039047807</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2630,18 +2630,18 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>feature_v23_B</t>
+          <t>feature_v42</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>0.0165668499523119</v>
+        <v>0.0578635244692798</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>0.4139337366486004</v>
+        <v>1.417736324282407</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2658,18 +2658,18 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>feature_v26_A</t>
+          <t>feature_v40</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>0.0112812146370807</v>
+        <v>0.0560061921275163</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>0.2818686317618306</v>
+        <v>1.372229114838562</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -2686,14 +2686,14 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>feature_v27_A</t>
+          <t>feature_v23_C</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>0.002365474025096</v>
+        <v>0.0479527567943108</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>0.0591029377927449</v>
+        <v>1.174908818298269</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
@@ -2714,14 +2714,14 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>feature_v19</t>
+          <t>feature_v26_A</t>
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>0.0015500830257324</v>
+        <v>0.0342769248966686</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>0.0387298527362749</v>
+        <v>0.8398320350587521</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -2742,18 +2742,18 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>feature_v25_C</t>
+          <t>feature_v23_B</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>0.0244703159298315</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>0.5995565613844884</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2770,14 +2770,14 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>feature_v25_A</t>
+          <t>feature_v54_F</t>
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>0.0225552990330472</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>0.5526360006152057</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -2798,18 +2798,18 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>feature_v3</t>
+          <t>feature_v23_A</t>
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>0</v>
+        <v>0.0018445621061432</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>0</v>
+        <v>0.045194321021052</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2826,18 +2826,18 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>feature_v23_A</t>
+          <t>feature_v9</t>
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>0</v>
+        <v>0.0001456326373357</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>0</v>
+        <v>0.0035682008976405</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_C</t>
+          <t>feature_v27_A</t>
         </is>
       </c>
       <c r="D60" s="3" t="n">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_D</t>
+          <t>feature_v19</t>
         </is>
       </c>
       <c r="D61" s="3" t="n">
@@ -2900,52 +2900,52 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>w2_predict_w3</t>
+          <t>w2_predict_w2</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>ridge</t>
+          <t>lasso</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>feature_v52</t>
+          <t>feature_v3</t>
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>0.354237683060036</v>
+        <v>0</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>14.76318848064694</v>
+        <v>0</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>w2_predict_w3</t>
+          <t>w2_predict_w2</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>ridge</t>
+          <t>lasso</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_A</t>
+          <t>feature_v25_C</t>
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>0.2476960701989291</v>
+        <v>0</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>10.32296659879236</v>
+        <v>0</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
@@ -2956,52 +2956,52 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>w2_predict_w3</t>
+          <t>w2_predict_w2</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>ridge</t>
+          <t>lasso</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>feature_v1_male</t>
+          <t>feature_v25_A</t>
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.1564319580538005</v>
+        <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>6.519448922528978</v>
+        <v>0</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>w2_predict_w3</t>
+          <t>w2_predict_w2</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>ridge</t>
+          <t>lasso</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>feature_v26_B</t>
+          <t>feature_v25_B</t>
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>0.1340378484258796</v>
+        <v>0</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>5.586153349801233</v>
+        <v>0</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
@@ -3012,24 +3012,24 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>w2_predict_w3</t>
+          <t>w2_predict_w2</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>ridge</t>
+          <t>lasso</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>feature_v28</t>
+          <t>feature_v34</t>
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0.1257324461054511</v>
+        <v>0</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>5.240017899713308</v>
+        <v>0</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
@@ -3040,28 +3040,28 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>w2_predict_w3</t>
+          <t>w2_predict_w2</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>ridge</t>
+          <t>lasso</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>feature_v5</t>
+          <t>feature_v54_C</t>
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0.1234199825015764</v>
+        <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>5.14364380494245</v>
+        <v>0</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3078,14 +3078,14 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>feature_v25_B</t>
+          <t>feature_v52</t>
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.1198502438322657</v>
+        <v>0.3062967191714441</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>4.994871589783294</v>
+        <v>13.25773649199624</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
@@ -3106,18 +3106,18 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_B</t>
+          <t>feature_v54_A</t>
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>0.1102643349864856</v>
+        <v>0.1890055787184754</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>4.595369826373872</v>
+        <v>8.180910866251336</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3134,14 +3134,14 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_E</t>
+          <t>feature_v1_male</t>
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0.1076726454754942</v>
+        <v>0.1532989426729192</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>4.487358729407664</v>
+        <v>6.635386079083672</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
@@ -3162,14 +3162,14 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>feature_v42</t>
+          <t>feature_v8_03-v8_06</t>
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0.0902387158744529</v>
+        <v>0.1454887740313764</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>3.760783322649255</v>
+        <v>6.297331012455067</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
@@ -3190,14 +3190,14 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>feature_v23_A</t>
+          <t>feature_v26_B</t>
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>0.0791275538025786</v>
+        <v>0.1235933459669911</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>3.297715197064503</v>
+        <v>5.349610069043333</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -3218,14 +3218,14 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_C</t>
+          <t>feature_v28</t>
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.0720191219985248</v>
+        <v>0.1185363235816402</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>3.001464618586984</v>
+        <v>5.130722088785271</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -3246,14 +3246,14 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>feature_v19</t>
+          <t>feature_v25_B</t>
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0.0715972277295709</v>
+        <v>0.1049822460549089</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>2.983881778281384</v>
+        <v>4.544047870636332</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
@@ -3274,18 +3274,18 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>feature_v25_C</t>
+          <t>feature_v5</t>
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.0708077718193022</v>
+        <v>0.1014071863233916</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>2.950980461008251</v>
+        <v>4.389305110113736</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -3302,18 +3302,18 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>feature_v34</t>
+          <t>feature_v54_E</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.0632083371889797</v>
+        <v>0.09979597687143819</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>2.634266878126128</v>
+        <v>4.31956557648375</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -3330,14 +3330,14 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>feature_v49</t>
+          <t>feature_v54_B</t>
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>0.0628034777719188</v>
+        <v>0.09404410122908829</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>2.617393981288604</v>
+        <v>4.070601592124767</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
@@ -3358,14 +3358,14 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>feature_v6</t>
+          <t>feature_v42</t>
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.0612485700234564</v>
+        <v>0.0749650558547372</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>2.552591739013669</v>
+        <v>3.244784858676816</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
@@ -3386,14 +3386,14 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>feature_v27_A</t>
+          <t>feature_v23_A</t>
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0.0601199194807188</v>
+        <v>0.07252893973920441</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>2.505554166536107</v>
+        <v>3.13934009383896</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
@@ -3414,18 +3414,18 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>feature_v36</t>
+          <t>feature_v9</t>
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.0537651428136538</v>
+        <v>0.0644128753721377</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>2.240712874446925</v>
+        <v>2.788044647313389</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>feature_v38</t>
+          <t>feature_v25_C</t>
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>0.0512804048594318</v>
+        <v>0.06433740331955889</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>2.137159084160364</v>
+        <v>2.78477791762622</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
@@ -3470,18 +3470,18 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>feature_v40</t>
+          <t>feature_v19</t>
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.050357583443687</v>
+        <v>0.0586058883938961</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>2.098699634061971</v>
+        <v>2.536695225817013</v>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -3498,14 +3498,14 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>feature_v22</t>
+          <t>feature_v27_A</t>
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.0334297655017529</v>
+        <v>0.0573797972243609</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>1.393216906521389</v>
+        <v>2.483625138468922</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
@@ -3526,14 +3526,14 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>feature_v27_B</t>
+          <t>feature_v49</t>
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0.0323071413421104</v>
+        <v>0.0503143113198175</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>1.346430489225066</v>
+        <v>2.177802893412754</v>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
@@ -3554,18 +3554,18 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_D</t>
+          <t>feature_v40</t>
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.0199674876573502</v>
+        <v>0.0478820557011842</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>0.832163820698017</v>
+        <v>2.07252522618783</v>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3582,18 +3582,18 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>feature_v23_B</t>
+          <t>feature_v54_C</t>
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.0155746284012133</v>
+        <v>0.0469426091776673</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>0.6490872812201087</v>
+        <v>2.031862255683932</v>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3610,14 +3610,14 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>feature_v25_A</t>
+          <t>feature_v6</t>
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.0126035522974446</v>
+        <v>0.0463721738003202</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>0.5252648913168592</v>
+        <v>2.007171550739268</v>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
@@ -3638,14 +3638,14 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>feature_v26_A</t>
+          <t>feature_v54_F</t>
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.0096554917462794</v>
+        <v>0.0451069776074339</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0.4024016962066017</v>
+        <v>1.952408842926607</v>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
@@ -3666,14 +3666,14 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>feature_v3</t>
+          <t>feature_v36</t>
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.0046481962578263</v>
+        <v>0.0417986180742434</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>0.1937179490802467</v>
+        <v>1.809209924471093</v>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
@@ -3694,14 +3694,14 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>feature_v23_C</t>
+          <t>feature_v12</t>
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.0042417549797614</v>
+        <v>0.0383385923818255</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>0.176779126698185</v>
+        <v>1.659446293278106</v>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
@@ -3722,18 +3722,18 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_F</t>
+          <t>feature_v38</t>
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.0011209081701101</v>
+        <v>0.0368130852192365</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0.0467149018192633</v>
+        <v>1.593416294546917</v>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3745,19 +3745,19 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>lasso</t>
+          <t>ridge</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>feature_v52</t>
+          <t>feature_v27_B</t>
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.3787585008935511</v>
+        <v>0.0268657466163929</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>15.31543991536995</v>
+        <v>1.162856037976406</v>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
@@ -3773,19 +3773,19 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>lasso</t>
+          <t>ridge</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_A</t>
+          <t>feature_v22</t>
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.2689489880013892</v>
+        <v>0.0253100722097945</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>10.87519370870169</v>
+        <v>1.095520281309423</v>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
@@ -3801,23 +3801,23 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>lasso</t>
+          <t>ridge</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>feature_v1_male</t>
+          <t>feature_v34</t>
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.1571260397244539</v>
+        <v>0.0242413192631874</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>6.353532435213204</v>
+        <v>1.049260416105869</v>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3829,23 +3829,23 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>lasso</t>
+          <t>ridge</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>feature_v26_B</t>
+          <t>feature_v23_B</t>
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.1410608725274857</v>
+        <v>0.0158599232157008</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>5.703922981286546</v>
+        <v>0.6864803623944861</v>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -3857,19 +3857,19 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>lasso</t>
+          <t>ridge</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>feature_v28</t>
+          <t>feature_v25_A</t>
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0.1300719624583147</v>
+        <v>0.0140234017930263</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>5.259576540209329</v>
+        <v>0.6069884332951875</v>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
@@ -3885,23 +3885,23 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>lasso</t>
+          <t>ridge</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>feature_v5</t>
+          <t>feature_v26_A</t>
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>0.1251367846090354</v>
+        <v>0.0131120640650243</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>5.060018194603919</v>
+        <v>0.5675421229143636</v>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3913,23 +3913,23 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>lasso</t>
+          <t>ridge</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>feature_v25_B</t>
+          <t>feature_v23_C</t>
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>0.1198561695860306</v>
+        <v>0.0037269530361656</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>4.846491786852718</v>
+        <v>0.1613173050145278</v>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3941,19 +3941,19 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>lasso</t>
+          <t>ridge</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_B</t>
+          <t>feature_v54_D</t>
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>0.1181859509123151</v>
+        <v>0.0028661032956467</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>4.778954995777482</v>
+        <v>0.1240563149200998</v>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
@@ -3969,19 +3969,19 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>lasso</t>
+          <t>ridge</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_E</t>
+          <t>feature_v3</t>
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0.110203475362766</v>
+        <v>0.0020712244355302</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>4.456176432744279</v>
+        <v>0.08965080610828791</v>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
@@ -4002,18 +4002,18 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>feature_v42</t>
+          <t>feature_v52</t>
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0.09382130712608561</v>
+        <v>0.3578208541738752</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>3.79374875727179</v>
+        <v>14.57807411709198</v>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -4030,14 +4030,14 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_C</t>
+          <t>feature_v54_A</t>
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>0.0811662740079286</v>
+        <v>0.2202619913718275</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>3.282031135381049</v>
+        <v>8.973752082757207</v>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
@@ -4058,18 +4058,18 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>feature_v23_A</t>
+          <t>feature_v1_male</t>
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0.0805335580729119</v>
+        <v>0.1598369168251421</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>3.256446698692803</v>
+        <v>6.511958129170749</v>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -4086,14 +4086,14 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>feature_v25_C</t>
+          <t>feature_v8_03-v8_06</t>
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>0.0728798290777847</v>
+        <v>0.1587276384392465</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>2.946961297634202</v>
+        <v>6.466764724880747</v>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
@@ -4114,18 +4114,18 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>feature_v19</t>
+          <t>feature_v26_B</t>
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>0.0702786968604172</v>
+        <v>0.1419914297508865</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>2.841782181936358</v>
+        <v>5.784910417475082</v>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -4142,14 +4142,14 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>feature_v34</t>
+          <t>feature_v28</t>
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.0624684235526094</v>
+        <v>0.1311443559517207</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>2.525966771097653</v>
+        <v>5.342986913148065</v>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
@@ -4170,18 +4170,18 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>feature_v6</t>
+          <t>feature_v54_E</t>
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0.0621311924063095</v>
+        <v>0.1112555901052562</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>2.51233052703564</v>
+        <v>4.53269344024065</v>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -4198,14 +4198,14 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>feature_v49</t>
+          <t>feature_v54_B</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>0.0612071514110522</v>
+        <v>0.1077028599039927</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>2.47496610007541</v>
+        <v>4.387950718881871</v>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
@@ -4226,18 +4226,18 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>feature_v27_A</t>
+          <t>feature_v25_B</t>
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>0.0568388817977077</v>
+        <v>0.1066102900621913</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>2.298331197784159</v>
+        <v>4.343438041808718</v>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -4254,18 +4254,18 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>feature_v36</t>
+          <t>feature_v5</t>
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0.053915569089398</v>
+        <v>0.1043760392071379</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>2.180124424781493</v>
+        <v>4.252411836429092</v>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -4282,14 +4282,14 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>feature_v40</t>
+          <t>feature_v42</t>
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0.051417365635829</v>
+        <v>0.0824962027616197</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>2.079107326025313</v>
+        <v>3.360999629309327</v>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
@@ -4310,14 +4310,14 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>feature_v38</t>
+          <t>feature_v23_A</t>
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0.0506276451621914</v>
+        <v>0.07579952583081449</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>2.047174269908025</v>
+        <v>3.088168542197617</v>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
@@ -4338,14 +4338,14 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>feature_v22</t>
+          <t>feature_v25_C</t>
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>0.0311563987897543</v>
+        <v>0.07004077793845109</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>1.259836947601332</v>
+        <v>2.853549870263736</v>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
@@ -4366,18 +4366,18 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>feature_v27_B</t>
+          <t>feature_v54_C</t>
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0.0309807527857525</v>
+        <v>0.0692453036163429</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>1.252734543789091</v>
+        <v>2.82114124038466</v>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -4394,14 +4394,14 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_D</t>
+          <t>feature_v9</t>
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0.022913286906408</v>
+        <v>0.06664023011096851</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0.926519320492698</v>
+        <v>2.715007251270191</v>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
@@ -4422,14 +4422,14 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>feature_v23_B</t>
+          <t>feature_v19</t>
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0.0113398569538653</v>
+        <v>0.0566409917166406</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0.4585372933309454</v>
+        <v>2.307625633551087</v>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
@@ -4450,14 +4450,14 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>feature_v25_A</t>
+          <t>feature_v40</t>
         </is>
       </c>
       <c r="D117" s="3" t="n">
-        <v>0.009129367961146001</v>
+        <v>0.0523744370641503</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>0.3691541870199036</v>
+        <v>2.133800801311424</v>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
@@ -4478,18 +4478,18 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>feature_v23_C</t>
+          <t>feature_v27_A</t>
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.0074597151906823</v>
+        <v>0.0507141367161706</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.3016402787505424</v>
+        <v>2.066158065436336</v>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -4506,14 +4506,14 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>feature_v3</t>
+          <t>feature_v6</t>
         </is>
       </c>
       <c r="D119" s="3" t="n">
-        <v>0.0061423761715103</v>
+        <v>0.0483214207346847</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>0.2483724932125172</v>
+        <v>1.968675790402971</v>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
@@ -4534,18 +4534,18 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>feature_v26_A</t>
+          <t>feature_v49</t>
         </is>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0.0043782074160153</v>
+        <v>0.0470073163296089</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0.1770367462613221</v>
+        <v>1.915137515058393</v>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -4562,18 +4562,354 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
+          <t>feature_v36</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0.0420091855490653</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>1.711507346174282</v>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>w2_predict_w3</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>lasso</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
           <t>feature_v54_F</t>
         </is>
       </c>
-      <c r="D121" s="3" t="n">
-        <v>0.0029154913944856</v>
-      </c>
-      <c r="E121" s="3" t="n">
-        <v>0.117890511158645</v>
-      </c>
-      <c r="F121" s="3" t="inlineStr">
-        <is>
-          <t>negative</t>
+      <c r="D122" s="3" t="n">
+        <v>0.0419936160620819</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>1.710873025584632</v>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>w2_predict_w3</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>lasso</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>feature_v38</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0.0339151386856178</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>1.381745640823214</v>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>w2_predict_w3</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>lasso</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>feature_v12</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0.0325853901251458</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>1.327570002803419</v>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>w2_predict_w3</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>lasso</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>feature_v27_B</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0.0274078050166864</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>1.116628637653148</v>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>w2_predict_w3</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>lasso</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>feature_v22</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0.019480570434593</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0.7936630756035521</v>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>w2_predict_w3</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>lasso</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>feature_v34</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>0.0153599818864716</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>0.6257850870518709</v>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>w2_predict_w3</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>lasso</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>feature_v23_B</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0.0103304390834306</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>0.4208751526460103</v>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>w2_predict_w3</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>lasso</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>feature_v25_A</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>0.0068516281704669</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>0.2791439965745734</v>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>w2_predict_w3</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>lasso</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>feature_v23_C</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>0.0029780390618103</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>0.1213290775544635</v>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>w2_predict_w3</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>lasso</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>feature_v3</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0.0014840478706468</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>0.0604619870508993</v>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>w2_predict_w3</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>lasso</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>feature_v26_A</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>0.0011097399601787</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>0.0452122094100302</v>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>w2_predict_w3</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>lasso</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>feature_v54_D</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -4588,12 +4924,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:H133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -4660,16 +4996,16 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.5472500636055357</v>
+        <v>0.494652632464277</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.6808218023326682</v>
+        <v>-0.6153864917696557</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.6808218023326682</v>
+        <v>0.6153864917696557</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>15.85505078243633</v>
+        <v>14.58186760401076</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -4694,16 +5030,16 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.4395763084105351</v>
+        <v>0.3393460116507707</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.5309076913222321</v>
+        <v>0.4090879938446025</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.5309076913222321</v>
+        <v>0.4090879938446025</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>12.36383496806257</v>
+        <v>9.693529260738488</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -4728,16 +5064,16 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.2769994738680235</v>
+        <v>0.2796881250635813</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-0.2771443473979836</v>
+        <v>-0.2798344047853434</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.2771443473979836</v>
+        <v>0.2798344047853434</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>6.454167135959478</v>
+        <v>6.630805674483995</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -4758,20 +5094,20 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>feature_v28</t>
+          <t>feature_v8_03-v8_06</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.2349111072939669</v>
+        <v>0.2584194533142128</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.2972268042288374</v>
+        <v>0.3278400636691858</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.2972268042288374</v>
+        <v>0.3278400636691858</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>6.921849533612321</v>
+        <v>7.768321969446013</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -4792,24 +5128,24 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_B</t>
+          <t>feature_v28</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.2315698780721876</v>
+        <v>0.2264350958355653</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-0.3247272544633885</v>
+        <v>0.2865023313530799</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.3247272544633885</v>
+        <v>0.2865023313530799</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>7.56228295321603</v>
+        <v>6.788805279129842</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -4826,20 +5162,20 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>feature_v5</t>
+          <t>feature_v54_B</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.2182297124850055</v>
+        <v>0.2025032452711542</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>-0.2667717969891616</v>
+        <v>-0.2839675151373934</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.2667717969891616</v>
+        <v>0.2839675151373934</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>6.212610075195882</v>
+        <v>6.728741636277774</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -4860,24 +5196,24 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>feature_v26_B</t>
+          <t>feature_v5</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.1694689025947285</v>
+        <v>0.1860715466031672</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.2259702649572769</v>
+        <v>-0.2274605061365779</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.2259702649572769</v>
+        <v>0.2274605061365779</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>5.262419643352697</v>
+        <v>5.389781917517881</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -4894,24 +5230,24 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_E</t>
+          <t>feature_v26_B</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.1591763352914828</v>
+        <v>0.1647490462578884</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-0.2186433461126733</v>
+        <v>0.2196767965352496</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.2186433461126733</v>
+        <v>0.2196767965352496</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>5.091789575452466</v>
+        <v>5.205343317723068</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -4928,24 +5264,24 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>feature_v22</t>
+          <t>feature_v54_E</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.1148639654906017</v>
+        <v>0.158030886900523</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.1441291664893662</v>
+        <v>-0.2170699673278155</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.1441291664893662</v>
+        <v>0.2170699673278155</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>3.356495409062302</v>
+        <v>5.143573293717893</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -4962,24 +5298,24 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>feature_v27_B</t>
+          <t>feature_v22</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.1047831335857813</v>
+        <v>0.098941448399296</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.1267433703640473</v>
+        <v>0.1241498883321071</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.1267433703640473</v>
+        <v>0.1241498883321071</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>2.951613133677524</v>
+        <v>2.94178903652167</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -4996,24 +5332,24 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>feature_v6</t>
+          <t>feature_v27_B</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.1016498667608825</v>
+        <v>0.0981756575961524</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.1330839946161186</v>
+        <v>-0.1187511129475481</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.1330839946161186</v>
+        <v>0.1187511129475481</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>3.099274267860499</v>
+        <v>2.813862556278261</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -5030,20 +5366,20 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>feature_v34</t>
+          <t>feature_v6</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.0939600314540152</v>
+        <v>0.0787759413549807</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.1008153313975246</v>
+        <v>0.1031365538316713</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.1008153313975246</v>
+        <v>0.1031365538316713</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2.347798195473862</v>
+        <v>2.443868354637677</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
@@ -5064,24 +5400,24 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>feature_v38</t>
+          <t>feature_v12</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.0845036030882171</v>
+        <v>0.0697560042452974</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.1442060122236839</v>
+        <v>-0.09235938549930101</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.1442060122236839</v>
+        <v>0.09235938549930101</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>3.358285000723213</v>
+        <v>2.188498365418633</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -5098,20 +5434,20 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>feature_v36</t>
+          <t>feature_v54_D</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.0730542166296702</v>
+        <v>0.06749084721972309</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.0997087125668607</v>
+        <v>0.084542135993254</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.0997087125668607</v>
+        <v>0.084542135993254</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>2.322027138059337</v>
+        <v>2.003265022065749</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -5136,16 +5472,16 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.06439463289189699</v>
+        <v>0.0669468190272904</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.0771390266012678</v>
+        <v>0.080196317952242</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.0771390266012678</v>
+        <v>0.080196317952242</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1.796421882907324</v>
+        <v>1.900288853182148</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
@@ -5166,24 +5502,24 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>feature_v49</t>
+          <t>feature_v38</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.0588681583509488</v>
+        <v>0.0605248669121098</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.0929488195496951</v>
+        <v>0.1032861248372195</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.0929488195496951</v>
+        <v>0.1032861248372195</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>2.164602028135158</v>
+        <v>2.447412508806596</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -5200,24 +5536,24 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_D</t>
+          <t>feature_v49</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0.0535086242150135</v>
+        <v>0.0521565991245638</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0.0670273610652735</v>
+        <v>-0.0823517238547483</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.0670273610652735</v>
+        <v>0.0823517238547483</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1.560940336900862</v>
+        <v>1.951362193145896</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -5238,20 +5574,20 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.0498195783255874</v>
+        <v>0.0512797729783281</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>-0.0621389189742859</v>
+        <v>0.0635983191716923</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.0621389189742859</v>
+        <v>0.0635983191716923</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1.447097775845899</v>
+        <v>1.506991593741977</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -5268,20 +5604,20 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>feature_v42</t>
+          <t>feature_v36</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.045183913004302</v>
+        <v>0.0506360441881407</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.0911089184456108</v>
+        <v>0.0691110658413045</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.0911089184456108</v>
+        <v>0.0691110658413045</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2.121754214889507</v>
+        <v>1.637618676308529</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
@@ -5302,20 +5638,20 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>feature_v25_B</t>
+          <t>feature_v26_A</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0.0427830008415498</v>
+        <v>0.0393377180101571</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-0.052884460127132</v>
+        <v>-0.0477933947739358</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.052884460127132</v>
+        <v>0.0477933947739358</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1.231578950680697</v>
+        <v>1.132486598683116</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -5336,24 +5672,24 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>feature_v27_A</t>
+          <t>feature_v23_B</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0.0358465838313504</v>
+        <v>0.0366184447118874</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>0.0449631836474659</v>
+        <v>-0.0452691952147773</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.0449631836474659</v>
+        <v>0.0452691952147773</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1.04710741875191</v>
+        <v>1.072674522418806</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -5370,24 +5706,24 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>feature_v26_A</t>
+          <t>feature_v40</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.0354559031414846</v>
+        <v>0.0344141050947741</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-0.0430771804167657</v>
+        <v>0.0654067112959775</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.0430771804167657</v>
+        <v>0.0654067112959775</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.003185974262123</v>
+        <v>1.549842281700093</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -5404,24 +5740,24 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>feature_v23_B</t>
+          <t>feature_v42</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0.0344902349140665</v>
+        <v>0.0337761558282428</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>-0.0426382166040368</v>
+        <v>0.0681062976212063</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.0426382166040368</v>
+        <v>0.0681062976212063</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.9929633381499696</v>
+        <v>1.613810228521422</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -5438,20 +5774,20 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>feature_v40</t>
+          <t>feature_v27_A</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.0337998508737061</v>
+        <v>0.0321784176540124</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0.064239272875335</v>
+        <v>0.0403621195612183</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.064239272875335</v>
+        <v>0.0403621195612183</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1.496011041619885</v>
+        <v>0.9563990947647248</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
@@ -5472,20 +5808,20 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>feature_v19</t>
+          <t>feature_v25_B</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.018713864121703</v>
+        <v>0.0302806712763348</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-0.0231898515089361</v>
+        <v>-0.0374302157688039</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.0231898515089361</v>
+        <v>0.0374302157688039</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.5400477365025439</v>
+        <v>0.8869262780869632</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
@@ -5506,24 +5842,24 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>feature_v25_A</t>
+          <t>feature_v54_C</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.017692178841651</v>
+        <v>0.025143792727723</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.022353135756453</v>
+        <v>-0.0352105922833573</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.022353135756453</v>
+        <v>0.0352105922833573</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.5205622107737417</v>
+        <v>0.834331272788002</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -5540,24 +5876,24 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>feature_v25_C</t>
+          <t>feature_v34</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.0136798908653501</v>
+        <v>0.0159199748049061</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>-0.0168052148996395</v>
+        <v>0.0170814921085077</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.0168052148996395</v>
+        <v>0.0170814921085077</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.3913616378480007</v>
+        <v>0.4047538575130874</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -5574,20 +5910,20 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>feature_v23_A</t>
+          <t>feature_v9</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.0114180732518955</v>
+        <v>0.0135627486543211</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.0135343892784774</v>
+        <v>-0.0183318701996152</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.0135343892784774</v>
+        <v>0.0183318701996152</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.3151903017563293</v>
+        <v>0.434382144814381</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
@@ -5608,24 +5944,24 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>feature_v3</t>
+          <t>feature_v23_A</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.0054276953735597</v>
+        <v>0.0131751806479891</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>0.0073195543830187</v>
+        <v>-0.0156171728601008</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.0073195543830187</v>
+        <v>0.0156171728601008</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.1704585635329875</v>
+        <v>0.3700561355191096</v>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -5642,24 +5978,24 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_C</t>
+          <t>feature_v25_A</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.0012639164282938</v>
+        <v>0.0117943487405759</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0.0017699496062033</v>
+        <v>0.0149015381834363</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.0017699496062033</v>
+        <v>0.0149015381834363</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.0412187752985537</v>
+        <v>0.3530988407985964</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -5671,25 +6007,25 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>lasso</t>
+          <t>ridge</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>feature_v52</t>
+          <t>feature_v25_C</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.6004290559593034</v>
+        <v>0.0110217235794421</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>-0.7469806204458977</v>
+        <v>-0.0135397595741134</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.7469806204458977</v>
+        <v>0.0135397595741134</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>18.66380635517925</v>
+        <v>0.3208308666836329</v>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
@@ -5705,29 +6041,29 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>lasso</t>
+          <t>ridge</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_A</t>
+          <t>feature_v19</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0.4938947897860538</v>
+        <v>0.009825327158107499</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>0.5965119993603074</v>
+        <v>-0.0121753517254081</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.5965119993603074</v>
+        <v>0.0121753517254081</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>14.90424803518439</v>
+        <v>0.2885005915252039</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -5739,29 +6075,29 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>lasso</t>
+          <t>ridge</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>feature_v1_male</t>
+          <t>feature_v3</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.2738699166624189</v>
+        <v>0.000506347643383</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>-0.2740131534022609</v>
+        <v>0.0006828384530402</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.2740131534022609</v>
+        <v>0.0006828384530402</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>6.846400420427281</v>
+        <v>0.0161801730300052</v>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -5778,20 +6114,20 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_B</t>
+          <t>feature_v52</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0.2445724763211721</v>
+        <v>0.5759948835566551</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-0.3429606191195953</v>
+        <v>-0.7165826024281782</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.3429606191195953</v>
+        <v>0.7165826024281782</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>8.569098591713896</v>
+        <v>17.55726416821722</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
@@ -5812,20 +6148,20 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>feature_v28</t>
+          <t>feature_v54_A</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.2397206432413257</v>
+        <v>0.4058518957833477</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.303312182719127</v>
+        <v>0.4892620869076461</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.303312182719127</v>
+        <v>0.4892620869076461</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>7.578456105136058</v>
+        <v>11.98759735196301</v>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
@@ -5846,20 +6182,20 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>feature_v5</t>
+          <t>feature_v1_male</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0.2215626057171446</v>
+        <v>0.283619005268492</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-0.2708460447466573</v>
+        <v>-0.2837673408804152</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.2708460447466573</v>
+        <v>0.2837673408804152</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>6.767268109580031</v>
+        <v>6.952692054297187</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
@@ -5880,20 +6216,20 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>feature_v26_B</t>
+          <t>feature_v8_03-v8_06</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>0.1613135828201915</v>
+        <v>0.2818086410683191</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>0.2150959408656728</v>
+        <v>0.3575124149729877</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.2150959408656728</v>
+        <v>0.3575124149729877</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>5.37431477901744</v>
+        <v>8.759548294681307</v>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
@@ -5914,24 +6250,24 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_E</t>
+          <t>feature_v28</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>0.148090003452642</v>
+        <v>0.2417667719532038</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>-0.2034152490156939</v>
+        <v>0.3059010952021421</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.2034152490156939</v>
+        <v>0.3059010952021421</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>5.082464944074746</v>
+        <v>7.494999626856387</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -5948,24 +6284,24 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>feature_v22</t>
+          <t>feature_v54_B</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0.1083921138161341</v>
+        <v>0.2212779365290952</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0.1360084074375641</v>
+        <v>-0.3102950064170995</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.1360084074375641</v>
+        <v>0.3102950064170995</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>3.3982602889694</v>
+        <v>7.602656524569627</v>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -5982,24 +6318,24 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>feature_v6</t>
+          <t>feature_v5</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.0945027290434621</v>
+        <v>0.1931275067105788</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.1237266814408501</v>
+        <v>-0.2360859638522293</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.1237266814408501</v>
+        <v>0.2360859638522293</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>3.091393217139333</v>
+        <v>5.784432415350495</v>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -6016,20 +6352,20 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>feature_v38</t>
+          <t>feature_v26_B</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>0.0880113889600795</v>
+        <v>0.1678673547804688</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>0.1501920742829295</v>
+        <v>0.2238347570358374</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.1501920742829295</v>
+        <v>0.2238347570358374</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>3.752648614666867</v>
+        <v>5.484260915615524</v>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
@@ -6050,20 +6386,20 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>feature_v27_B</t>
+          <t>feature_v54_E</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>0.0872974870148705</v>
+        <v>0.1553179807473401</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>-0.105593117422073</v>
+        <v>-0.2133435410475827</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.105593117422073</v>
+        <v>0.2133435410475827</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>2.638314090168575</v>
+        <v>5.227211623702142</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
@@ -6084,20 +6420,20 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>feature_v34</t>
+          <t>feature_v22</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>0.0854442119913818</v>
+        <v>0.0917143918773862</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>0.0916781999176671</v>
+        <v>0.1150815122907136</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.0916781999176671</v>
+        <v>0.1150815122907136</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>2.290640645045595</v>
+        <v>2.819656108478448</v>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
@@ -6118,24 +6454,24 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>feature_v36</t>
+          <t>feature_v27_B</t>
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>0.0719368967200379</v>
+        <v>0.0887053141363764</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>0.0981837283174256</v>
+        <v>-0.1072959940985359</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.0981837283174256</v>
+        <v>0.1072959940985359</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>2.453185587936797</v>
+        <v>2.628900152189061</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -6152,24 +6488,24 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>feature_v49</t>
+          <t>feature_v6</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0.0526768436304064</v>
+        <v>0.0742122660934303</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>-0.083173154557692</v>
+        <v>0.0971616110866243</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.083173154557692</v>
+        <v>0.0971616110866243</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>2.078136444406714</v>
+        <v>2.380593761384857</v>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -6186,20 +6522,20 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>feature_v42</t>
+          <t>feature_v38</t>
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>0.0413585497765661</v>
+        <v>0.0631345679499228</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>0.08339544957656291</v>
+        <v>0.1077395986064514</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.08339544957656291</v>
+        <v>0.1077395986064514</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>2.083690632925622</v>
+        <v>2.639769075751109</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
@@ -6220,24 +6556,24 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>feature_v23_C</t>
+          <t>feature_v12</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.035188824342876</v>
+        <v>0.0576756311915516</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.0421530729371397</v>
+        <v>-0.07636454972971329</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.0421530729371397</v>
+        <v>0.07636454972971329</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.053222492043894</v>
+        <v>1.871037013944137</v>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -6254,24 +6590,24 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_F</t>
+          <t>feature_v54_D</t>
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>0.0276979379867549</v>
+        <v>0.0472607187128238</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>-0.0345470592517995</v>
+        <v>0.0592009475825757</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.0345470592517995</v>
+        <v>0.0592009475825757</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.8631811942210765</v>
+        <v>1.450505039047807</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -6288,20 +6624,20 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>feature_v40</t>
+          <t>feature_v36</t>
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>0.0274461073852815</v>
+        <v>0.0471583797153143</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>0.0521634840424822</v>
+        <v>0.0643645438289913</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.0521634840424822</v>
+        <v>0.0643645438289913</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>1.303339254503303</v>
+        <v>1.577020283834842</v>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
@@ -6322,20 +6658,20 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>feature_v25_B</t>
+          <t>feature_v49</t>
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>0.013414114694519</v>
+        <v>0.0459130811019916</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>-0.0165813103276785</v>
+        <v>-0.0724936333981769</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.0165813103276785</v>
+        <v>0.0724936333981769</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.4142950387202719</v>
+        <v>1.776194213720472</v>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
@@ -6356,24 +6692,24 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>feature_v23_B</t>
+          <t>feature_v23_C</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>0.0134009954484641</v>
+        <v>0.040030323248509</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>-0.0165668499523119</v>
+        <v>0.0479527567943108</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.0165668499523119</v>
+        <v>0.0479527567943108</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.4139337366486004</v>
+        <v>1.174908818298269</v>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -6390,24 +6726,24 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>feature_v26_A</t>
+          <t>feature_v40</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>0.009285325771576</v>
+        <v>0.0294679696264279</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>-0.0112812146370807</v>
+        <v>0.0560061921275163</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.0112812146370807</v>
+        <v>0.0560061921275163</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.2818686317618306</v>
+        <v>1.372229114838562</v>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -6424,20 +6760,20 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>feature_v27_A</t>
+          <t>feature_v42</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>0.0018858576297959</v>
+        <v>0.0286964273130185</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>0.002365474025096</v>
+        <v>0.0578635244692798</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.002365474025096</v>
+        <v>0.0578635244692798</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.0591029377927449</v>
+        <v>1.417736324282407</v>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
@@ -6458,20 +6794,20 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>feature_v19</t>
+          <t>feature_v26_A</t>
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>0.0012508938709563</v>
+        <v>0.0282126015994121</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>-0.0015500830257324</v>
+        <v>-0.0342769248966686</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.0015500830257324</v>
+        <v>0.0342769248966686</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.0387298527362749</v>
+        <v>0.8398320350587521</v>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
@@ -6492,24 +6828,24 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>feature_v25_C</t>
+          <t>feature_v23_B</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>0.019794142721284</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>-0.0244703159298315</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>0.0244703159298315</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>0.5995565613844884</v>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -6526,20 +6862,20 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>feature_v25_A</t>
+          <t>feature_v54_F</t>
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>0.0181864965762774</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>0.0225552990330472</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>0.0225552990330472</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>0.5526360006152057</v>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
@@ -6560,24 +6896,24 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>feature_v3</t>
+          <t>feature_v23_A</t>
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>0</v>
+        <v>0.0015561356195884</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>0</v>
+        <v>-0.0018445621061432</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0</v>
+        <v>0.0018445621061432</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0</v>
+        <v>0.045194321021052</v>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -6594,24 +6930,24 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>feature_v23_A</t>
+          <t>feature_v9</t>
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>0</v>
+        <v>0.0001077456273987</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>0</v>
+        <v>-0.0001456326373357</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0</v>
+        <v>0.0001456326373357</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0</v>
+        <v>0.0035682008976405</v>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6964,7 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_C</t>
+          <t>feature_v27_A</t>
         </is>
       </c>
       <c r="D60" s="3" t="n">
@@ -6662,7 +6998,7 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_D</t>
+          <t>feature_v19</t>
         </is>
       </c>
       <c r="D61" s="3" t="n">
@@ -6686,64 +7022,64 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>w2_predict_w3</t>
+          <t>w2_predict_w2</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>ridge</t>
+          <t>lasso</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>feature_v52</t>
+          <t>feature_v3</t>
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>0.2676174774994347</v>
+        <v>0</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>-0.354237683060036</v>
+        <v>0</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.354237683060036</v>
+        <v>0</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>14.76318848064694</v>
+        <v>0</v>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>w2_predict_w3</t>
+          <t>w2_predict_w2</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>ridge</t>
+          <t>lasso</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_A</t>
+          <t>feature_v25_C</t>
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>0.2142142375244317</v>
+        <v>0</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>0.2476960701989291</v>
+        <v>0</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.2476960701989291</v>
+        <v>0</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>10.32296659879236</v>
+        <v>0</v>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
@@ -6754,64 +7090,64 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>w2_predict_w3</t>
+          <t>w2_predict_w2</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>ridge</t>
+          <t>lasso</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>feature_v1_male</t>
+          <t>feature_v25_A</t>
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.15638571138247</v>
+        <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>-0.1564319580538005</v>
+        <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.1564319580538005</v>
+        <v>0</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>6.519448922528978</v>
+        <v>0</v>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>w2_predict_w3</t>
+          <t>w2_predict_w2</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>ridge</t>
+          <t>lasso</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>feature_v28</t>
+          <t>feature_v25_B</t>
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>0.1012390007368136</v>
+        <v>0</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>0.1257324461054511</v>
+        <v>0</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.1257324461054511</v>
+        <v>0</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>5.240017899713308</v>
+        <v>0</v>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
@@ -6822,68 +7158,68 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>w2_predict_w3</t>
+          <t>w2_predict_w2</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>ridge</t>
+          <t>lasso</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>feature_v5</t>
+          <t>feature_v34</t>
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0.1002275722764337</v>
+        <v>0</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>-0.1234199825015764</v>
+        <v>0</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.1234199825015764</v>
+        <v>0</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>5.14364380494245</v>
+        <v>0</v>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>w2_predict_w3</t>
+          <t>w2_predict_w2</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>ridge</t>
+          <t>lasso</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>feature_v25_B</t>
+          <t>feature_v54_C</t>
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0.0950775319709399</v>
+        <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>-0.1198502438322657</v>
+        <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.1198502438322657</v>
+        <v>0</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>4.994871589783294</v>
+        <v>0</v>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -6900,24 +7236,24 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>feature_v26_B</t>
+          <t>feature_v52</t>
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.09368968440918771</v>
+        <v>0.2313993097598337</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.1340378484258796</v>
+        <v>-0.3062967191714441</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.1340378484258796</v>
+        <v>0.3062967191714441</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>5.586153349801233</v>
+        <v>13.25773649199624</v>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -6934,24 +7270,24 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_B</t>
+          <t>feature_v54_A</t>
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>0.08692439181599459</v>
+        <v>0.1638467526220544</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>-0.1102643349864856</v>
+        <v>0.1890055787184754</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.1102643349864856</v>
+        <v>0.1890055787184754</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>4.595369826373872</v>
+        <v>8.180910866251336</v>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -6968,20 +7304,20 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_E</t>
+          <t>feature_v1_male</t>
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0.0838542218971785</v>
+        <v>0.1532536222287772</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>-0.1076726454754942</v>
+        <v>-0.1532989426729192</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.1076726454754942</v>
+        <v>0.1532989426729192</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>4.487358729407664</v>
+        <v>6.635386079083672</v>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
@@ -7002,20 +7338,20 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>feature_v23_A</t>
+          <t>feature_v8_03-v8_06</t>
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0.06886275466632399</v>
+        <v>0.124457277126052</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0.0791275538025786</v>
+        <v>0.1454887740313764</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.0791275538025786</v>
+        <v>0.1454887740313764</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>3.297715197064503</v>
+        <v>6.297331012455067</v>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
@@ -7036,24 +7372,24 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>feature_v19</t>
+          <t>feature_v28</t>
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>0.0594000405952064</v>
+        <v>0.0954447266567623</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>-0.0715972277295709</v>
+        <v>0.1185363235816402</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.0715972277295709</v>
+        <v>0.1185363235816402</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>2.983881778281384</v>
+        <v>5.130722088785271</v>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -7070,20 +7406,20 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>feature_v25_C</t>
+          <t>feature_v26_B</t>
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.0571733861227537</v>
+        <v>0.0863891931623036</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>0.0708077718193022</v>
+        <v>0.1235933459669911</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.0708077718193022</v>
+        <v>0.1235933459669911</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>2.950980461008251</v>
+        <v>5.349610069043333</v>
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
@@ -7104,24 +7440,24 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>feature_v42</t>
+          <t>feature_v25_B</t>
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0.0560502017778933</v>
+        <v>0.083282707957074</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>0.0902387158744529</v>
+        <v>-0.1049822460549089</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.0902387158744529</v>
+        <v>0.1049822460549089</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>3.760783322649255</v>
+        <v>4.544047870636332</v>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -7138,24 +7474,24 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>feature_v34</t>
+          <t>feature_v5</t>
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.0524537299462523</v>
+        <v>0.0823513007421447</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.0632083371889797</v>
+        <v>-0.1014071863233916</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.0632083371889797</v>
+        <v>0.1014071863233916</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>2.634266878126128</v>
+        <v>4.389305110113736</v>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -7172,24 +7508,24 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_C</t>
+          <t>feature_v54_E</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.0509997142587084</v>
+        <v>0.0777199626893897</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>0.0720191219985248</v>
+        <v>-0.09979597687143819</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.0720191219985248</v>
+        <v>0.09979597687143819</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>3.001464618586984</v>
+        <v>4.31956557648375</v>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -7206,24 +7542,24 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>feature_v6</t>
+          <t>feature_v54_B</t>
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>0.0483978626464838</v>
+        <v>0.07413753780152189</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>0.0612485700234564</v>
+        <v>-0.09404410122908829</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.0612485700234564</v>
+        <v>0.09404410122908829</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>2.552591739013669</v>
+        <v>4.070601592124767</v>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -7240,20 +7576,20 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>feature_v27_A</t>
+          <t>feature_v23_A</t>
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.0466117239552988</v>
+        <v>0.0631201439125826</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>0.0601199194807188</v>
+        <v>0.07252893973920441</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.0601199194807188</v>
+        <v>0.07252893973920441</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>2.505554166536107</v>
+        <v>3.13934009383896</v>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
@@ -7274,24 +7610,24 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>feature_v49</t>
+          <t>feature_v25_C</t>
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0.0414216701052477</v>
+        <v>0.0519489189902985</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>-0.0628034777719188</v>
+        <v>0.06433740331955889</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.0628034777719188</v>
+        <v>0.06433740331955889</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>2.617393981288604</v>
+        <v>2.78477791762622</v>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -7308,24 +7644,24 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>feature_v36</t>
+          <t>feature_v19</t>
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.0364881811265379</v>
+        <v>0.0486218846749804</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.0537651428136538</v>
+        <v>-0.0586058883938961</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.0537651428136538</v>
+        <v>0.0586058883938961</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>2.240712874446925</v>
+        <v>2.536695225817013</v>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -7342,24 +7678,24 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>feature_v38</t>
+          <t>feature_v9</t>
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>0.0336093271745953</v>
+        <v>0.0481754304919011</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>0.0512804048594318</v>
+        <v>-0.0644128753721377</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.0512804048594318</v>
+        <v>0.0644128753721377</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>2.137159084160364</v>
+        <v>2.788044647313389</v>
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -7376,20 +7712,20 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>feature_v22</t>
+          <t>feature_v42</t>
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.0267024256234199</v>
+        <v>0.046563234707317</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>0.0334297655017529</v>
+        <v>0.0749650558547372</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.0334297655017529</v>
+        <v>0.0749650558547372</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>1.393216906521389</v>
+        <v>3.244784858676816</v>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
@@ -7410,24 +7746,24 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>feature_v27_B</t>
+          <t>feature_v27_A</t>
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.0259463432968421</v>
+        <v>0.0444872729693302</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>-0.0323071413421104</v>
+        <v>0.0573797972243609</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.0323071413421104</v>
+        <v>0.0573797972243609</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>1.346430489225066</v>
+        <v>2.483625138468922</v>
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -7444,20 +7780,20 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>feature_v40</t>
+          <t>feature_v6</t>
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0.0179465902446967</v>
+        <v>0.0366427183091342</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>0.050357583443687</v>
+        <v>0.0463721738003202</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.050357583443687</v>
+        <v>0.0463721738003202</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>2.098699634061971</v>
+        <v>2.007171550739268</v>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
@@ -7478,24 +7814,24 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_D</t>
+          <t>feature_v54_F</t>
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.0157336054071535</v>
+        <v>0.0363206834482757</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>-0.0199674876573502</v>
+        <v>0.0451069776074339</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.0199674876573502</v>
+        <v>0.0451069776074339</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.832163820698017</v>
+        <v>1.952408842926607</v>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -7512,24 +7848,24 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>feature_v23_B</t>
+          <t>feature_v54_C</t>
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.0127864440119427</v>
+        <v>0.0332420000158887</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>-0.0155746284012133</v>
+        <v>0.0469426091776673</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.0155746284012133</v>
+        <v>0.0469426091776673</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.6490872812201087</v>
+        <v>2.031862255683932</v>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -7546,24 +7882,24 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>feature_v25_A</t>
+          <t>feature_v49</t>
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.009998191671475301</v>
+        <v>0.0331845126894236</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>0.0126035522974446</v>
+        <v>-0.0503143113198175</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.0126035522974446</v>
+        <v>0.0503143113198175</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.5252648913168592</v>
+        <v>2.177802893412754</v>
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -7580,20 +7916,20 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>feature_v26_A</t>
+          <t>feature_v36</t>
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.0077423675404703</v>
+        <v>0.0283669951815825</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0.0096554917462794</v>
+        <v>0.0417986180742434</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.0096554917462794</v>
+        <v>0.0417986180742434</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.4024016962066017</v>
+        <v>1.809209924471093</v>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
@@ -7614,24 +7950,24 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>feature_v3</t>
+          <t>feature_v12</t>
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.0035254544513514</v>
+        <v>0.0280596401542396</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>0.0046481962578263</v>
+        <v>-0.0383385923818255</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>0.0046481962578263</v>
+        <v>0.0383385923818255</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>0.1937179490802467</v>
+        <v>1.659446293278106</v>
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -7648,24 +7984,24 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>feature_v23_C</t>
+          <t>feature_v38</t>
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.00347726987538</v>
+        <v>0.0241274036121816</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>-0.0042417549797614</v>
+        <v>0.0368130852192365</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.0042417549797614</v>
+        <v>0.0368130852192365</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.176779126698185</v>
+        <v>1.593416294546917</v>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -7682,20 +8018,20 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_F</t>
+          <t>feature_v27_B</t>
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.0008811136450667</v>
+        <v>0.0215762786702003</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>-0.0011209081701101</v>
+        <v>-0.0268657466163929</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.0011209081701101</v>
+        <v>0.0268657466163929</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.0467149018192633</v>
+        <v>1.162856037976406</v>
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
@@ -7711,29 +8047,29 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>lasso</t>
+          <t>ridge</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>feature_v52</t>
+          <t>feature_v22</t>
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.286142326008324</v>
+        <v>0.0202167233470418</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>-0.3787585008935511</v>
+        <v>0.0253100722097945</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.3787585008935511</v>
+        <v>0.0253100722097945</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>15.31543991536995</v>
+        <v>1.095520281309423</v>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -7745,25 +8081,25 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>lasso</t>
+          <t>ridge</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_A</t>
+          <t>feature_v34</t>
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.2325943336582444</v>
+        <v>0.0201167705198519</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>0.2689489880013892</v>
+        <v>0.0242413192631874</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.2689489880013892</v>
+        <v>0.0242413192631874</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>10.87519370870169</v>
+        <v>1.049260416105869</v>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
@@ -7779,29 +8115,29 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>lasso</t>
+          <t>ridge</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>feature_v1_male</t>
+          <t>feature_v40</t>
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.1570795878586876</v>
+        <v>0.0170643540650407</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>-0.1571260397244539</v>
+        <v>0.0478820557011842</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.1571260397244539</v>
+        <v>0.0478820557011842</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>6.353532435213204</v>
+        <v>2.07252522618783</v>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -7813,29 +8149,29 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>lasso</t>
+          <t>ridge</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>feature_v28</t>
+          <t>feature_v23_B</t>
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.104733152905591</v>
+        <v>0.0130206650847264</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>0.1300719624583147</v>
+        <v>-0.0158599232157008</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.1300719624583147</v>
+        <v>0.0158599232157008</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>5.259576540209329</v>
+        <v>0.6864803623944861</v>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -7847,29 +8183,29 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>lasso</t>
+          <t>ridge</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>feature_v5</t>
+          <t>feature_v25_A</t>
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0.1016217622918747</v>
+        <v>0.0111245350282092</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>-0.1251367846090354</v>
+        <v>0.0140234017930263</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.1251367846090354</v>
+        <v>0.0140234017930263</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>5.060018194603919</v>
+        <v>0.6069884332951875</v>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -7881,25 +8217,25 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>lasso</t>
+          <t>ridge</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>feature_v26_B</t>
+          <t>feature_v26_A</t>
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>0.0985986330338111</v>
+        <v>0.0105140599643441</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>0.1410608725274857</v>
+        <v>0.0131120640650243</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>0.1410608725274857</v>
+        <v>0.0131120640650243</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>5.703922981286546</v>
+        <v>0.5675421229143636</v>
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
@@ -7915,29 +8251,29 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>lasso</t>
+          <t>ridge</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>feature_v25_B</t>
+          <t>feature_v23_C</t>
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>0.0950822328878935</v>
+        <v>0.0030552499098718</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>-0.1198561695860306</v>
+        <v>0.0037269530361656</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>0.1198561695860306</v>
+        <v>0.0037269530361656</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>4.846491786852718</v>
+        <v>0.1613173050145278</v>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -7949,25 +8285,25 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>lasso</t>
+          <t>ridge</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_B</t>
+          <t>feature_v54_D</t>
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>0.0931692183651868</v>
+        <v>0.0022583781737432</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>-0.1181859509123151</v>
+        <v>-0.0028661032956467</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.1181859509123151</v>
+        <v>0.0028661032956467</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>4.778954995777482</v>
+        <v>0.1240563149200998</v>
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
@@ -7983,25 +8319,25 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>lasso</t>
+          <t>ridge</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_E</t>
+          <t>feature_v3</t>
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0.08582520319901379</v>
+        <v>0.0015709335408747</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>-0.110203475362766</v>
+        <v>-0.0020712244355302</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0.110203475362766</v>
+        <v>0.0020712244355302</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>4.456176432744279</v>
+        <v>0.08965080610828791</v>
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
@@ -8022,24 +8358,24 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>feature_v23_A</t>
+          <t>feature_v52</t>
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0.0700863654374763</v>
+        <v>0.2703244713083705</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0.0805335580729119</v>
+        <v>-0.3578208541738752</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.0805335580729119</v>
+        <v>0.3578208541738752</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>3.256446698692803</v>
+        <v>14.57807411709198</v>
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -8056,20 +8392,20 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>feature_v25_C</t>
+          <t>feature_v54_A</t>
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>0.0588464585364709</v>
+        <v>0.190942575647967</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>0.0728798290777847</v>
+        <v>0.2202619913718275</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>0.0728798290777847</v>
+        <v>0.2202619913718275</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>2.946961297634202</v>
+        <v>8.973752082757207</v>
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
@@ -8090,20 +8426,20 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>feature_v19</t>
+          <t>feature_v1_male</t>
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0.0583061324979612</v>
+        <v>0.1597896635307925</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>-0.0702786968604172</v>
+        <v>-0.1598369168251421</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0.0702786968604172</v>
+        <v>0.1598369168251421</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>2.841782181936358</v>
+        <v>6.511958129170749</v>
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
@@ -8124,20 +8460,20 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>feature_v42</t>
+          <t>feature_v8_03-v8_06</t>
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>0.0582754657413247</v>
+        <v>0.1357823640780479</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>0.09382130712608561</v>
+        <v>0.1587276384392465</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>0.09382130712608561</v>
+        <v>0.1587276384392465</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>3.79374875727179</v>
+        <v>6.466764724880747</v>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
@@ -8158,20 +8494,20 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_C</t>
+          <t>feature_v28</t>
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>0.0574771903208318</v>
+        <v>0.1055966376227967</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>0.0811662740079286</v>
+        <v>0.1311443559517207</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>0.0811662740079286</v>
+        <v>0.1311443559517207</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>3.282031135381049</v>
+        <v>5.342986913148065</v>
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
@@ -8192,20 +8528,20 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>feature_v34</t>
+          <t>feature_v26_B</t>
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.0518397092048154</v>
+        <v>0.0992490732908641</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.0624684235526094</v>
+        <v>0.1419914297508865</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.0624684235526094</v>
+        <v>0.1419914297508865</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>2.525966771097653</v>
+        <v>5.784910417475082</v>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
@@ -8226,24 +8562,24 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>feature_v6</t>
+          <t>feature_v54_E</t>
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0.0490952999391048</v>
+        <v>0.08664457809863151</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0.0621311924063095</v>
+        <v>-0.1112555901052562</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0.0621311924063095</v>
+        <v>0.1112555901052562</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>2.51233052703564</v>
+        <v>4.53269344024065</v>
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -8260,24 +8596,24 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>feature_v27_A</t>
+          <t>feature_v54_B</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>0.0440678944876541</v>
+        <v>0.08490511093315201</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>0.0568388817977077</v>
+        <v>-0.1077028599039927</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>0.0568388817977077</v>
+        <v>0.1077028599039927</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>2.298331197784159</v>
+        <v>4.387950718881871</v>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -8294,20 +8630,20 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>feature_v49</t>
+          <t>feature_v5</t>
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>0.040368822297356</v>
+        <v>0.0847622629781824</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>-0.0612071514110522</v>
+        <v>-0.1043760392071379</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>0.0612071514110522</v>
+        <v>0.1043760392071379</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>2.47496610007541</v>
+        <v>4.252411836429092</v>
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
@@ -8328,24 +8664,24 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>feature_v36</t>
+          <t>feature_v25_B</t>
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0.0365902692250419</v>
+        <v>0.0845742397988377</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0.053915569089398</v>
+        <v>-0.1066102900621913</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0.053915569089398</v>
+        <v>0.1066102900621913</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>2.180124424781493</v>
+        <v>4.343438041808718</v>
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -8362,20 +8698,20 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>feature_v38</t>
+          <t>feature_v23_A</t>
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0.0331815065618082</v>
+        <v>0.0659664541650591</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0.0506276451621914</v>
+        <v>0.07579952583081449</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0.0506276451621914</v>
+        <v>0.07579952583081449</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>2.047174269908025</v>
+        <v>3.088168542197617</v>
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
@@ -8396,20 +8732,20 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>feature_v22</t>
+          <t>feature_v25_C</t>
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0.0248865467313374</v>
+        <v>0.0565540806965698</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0.0311563987897543</v>
+        <v>0.07004077793845109</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0.0311563987897543</v>
+        <v>0.07004077793845109</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>1.259836947601332</v>
+        <v>2.853549870263736</v>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
@@ -8430,24 +8766,24 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>feature_v27_B</t>
+          <t>feature_v42</t>
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>0.0248811010191728</v>
+        <v>0.0512410750296132</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>-0.0309807527857525</v>
+        <v>0.0824962027616197</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>0.0309807527857525</v>
+        <v>0.0824962027616197</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>1.252734543789091</v>
+        <v>3.360999629309327</v>
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -8464,24 +8800,24 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>feature_v40</t>
+          <t>feature_v9</t>
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0.0183242786771107</v>
+        <v>0.049841305098204</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>0.051417365635829</v>
+        <v>-0.06664023011096851</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0.051417365635829</v>
+        <v>0.06664023011096851</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>2.079107326025313</v>
+        <v>2.715007251270191</v>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -8498,24 +8834,24 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_D</t>
+          <t>feature_v54_C</t>
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0.0180547808994693</v>
+        <v>0.0490354589196926</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>-0.022913286906408</v>
+        <v>0.0692453036163429</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0.022913286906408</v>
+        <v>0.0692453036163429</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0.926519320492698</v>
+        <v>2.82114124038466</v>
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -8532,20 +8868,20 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>feature_v23_B</t>
+          <t>feature_v19</t>
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0.0093097852679901</v>
+        <v>0.0469917245962251</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>-0.0113398569538653</v>
+        <v>-0.0566409917166406</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0.0113398569538653</v>
+        <v>0.0566409917166406</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0.4585372933309454</v>
+        <v>2.307625633551087</v>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
@@ -8566,20 +8902,20 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>feature_v25_A</t>
+          <t>feature_v27_A</t>
         </is>
       </c>
       <c r="D117" s="3" t="n">
-        <v>0.0072421781225497</v>
+        <v>0.0393193031804294</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>0.009129367961146001</v>
+        <v>0.0507141367161706</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>0.009129367961146001</v>
+        <v>0.0507141367161706</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>0.3691541870199036</v>
+        <v>2.066158065436336</v>
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
@@ -8600,24 +8936,24 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>feature_v23_C</t>
+          <t>feature_v6</t>
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.0061152619694532</v>
+        <v>0.0381829891327198</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>-0.0074597151906823</v>
+        <v>0.0483214207346847</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.0074597151906823</v>
+        <v>0.0483214207346847</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.3016402787505424</v>
+        <v>1.968675790402971</v>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -8634,20 +8970,20 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>feature_v3</t>
+          <t>feature_v54_F</t>
         </is>
       </c>
       <c r="D119" s="3" t="n">
-        <v>0.0046587248503685</v>
+        <v>0.0338137671096794</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>0.0061423761715103</v>
+        <v>0.0419936160620819</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>0.0061423761715103</v>
+        <v>0.0419936160620819</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>0.2483724932125172</v>
+        <v>1.710873025584632</v>
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
@@ -8668,24 +9004,24 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>feature_v26_A</t>
+          <t>feature_v49</t>
         </is>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0.0035107161679533</v>
+        <v>0.0310034032925593</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0.0043782074160153</v>
+        <v>-0.0470073163296089</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>0.0043782074160153</v>
+        <v>0.0470073163296089</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>0.1770367462613221</v>
+        <v>1.915137515058393</v>
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>positive</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -8702,24 +9038,432 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>feature_v54_F</t>
+          <t>feature_v36</t>
         </is>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0.0022917838572837</v>
+        <v>0.028509898627171</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>-0.0029154913944856</v>
+        <v>0.0420091855490653</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>0.0029154913944856</v>
+        <v>0.0420091855490653</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0.117890511158645</v>
+        <v>1.711507346174282</v>
       </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>w2_predict_w3</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>lasso</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>feature_v12</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0.0238489277877229</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>-0.0325853901251458</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>0.0325853901251458</v>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>1.327570002803419</v>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>w2_predict_w3</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>lasso</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>feature_v38</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0.022228080986905</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>0.0339151386856178</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>0.0339151386856178</v>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>1.381745640823214</v>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>w2_predict_w3</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>lasso</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>feature_v27_B</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0.0220116137929218</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>-0.0274078050166864</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>0.0274078050166864</v>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>1.116628637653148</v>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>w2_predict_w3</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>lasso</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>feature_v40</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0.0186653627320708</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0.0523744370641503</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>0.0523744370641503</v>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>2.133800801311424</v>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>w2_predict_w3</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>lasso</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>feature_v22</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0.0155603389770783</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0.019480570434593</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>0.019480570434593</v>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>0.7936630756035521</v>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>w2_predict_w3</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>lasso</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>feature_v34</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>0.0127465517633134</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>0.0153599818864716</v>
+      </c>
+      <c r="F127" s="3" t="n">
+        <v>0.0153599818864716</v>
+      </c>
+      <c r="G127" s="3" t="n">
+        <v>0.6257850870518709</v>
+      </c>
+      <c r="H127" s="3" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>w2_predict_w3</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>lasso</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>feature_v23_B</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0.0084810743188441</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>-0.0103304390834306</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>0.0103304390834306</v>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>0.4208751526460103</v>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>w2_predict_w3</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>lasso</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>feature_v25_A</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>0.0054352844415061</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>0.0068516281704669</v>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>0.0068516281704669</v>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>0.2791439965745734</v>
+      </c>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>w2_predict_w3</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>lasso</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>feature_v23_C</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>0.0024413115719192</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>-0.0029780390618103</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>0.0029780390618103</v>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>0.1213290775544635</v>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>w2_predict_w3</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>lasso</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>feature_v3</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0.0011255856855831</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>0.0014840478706468</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>0.0014840478706468</v>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>0.0604619870508993</v>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>w2_predict_w3</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>lasso</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>feature_v26_A</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>0.0008898578002888</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>0.0011097399601787</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>0.0011097399601787</v>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>0.0452122094100302</v>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>w2_predict_w3</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>lasso</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>feature_v54_D</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>positive</t>
         </is>
       </c>
     </row>
